--- a/preview/pr-23/CodeSystem-mhi-an-subtyp.xlsx
+++ b/preview/pr-23/CodeSystem-mhi-an-subtyp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T14:08:38+00:00</t>
+    <t>2026-10-01T14:23:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
